--- a/output/daily_ratings/uk_ratings_2026-06-03.xlsx
+++ b/output/daily_ratings/uk_ratings_2026-06-03.xlsx
@@ -522,34 +522,36 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Boston Max (IRE)</t>
+          <t>Meriden</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>3</v>
       </c>
       <c r="J2" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="K2" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
         <v>75.65000000000001</v>
       </c>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>94.8</v>
+      </c>
       <c r="O2" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -576,34 +578,38 @@
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Aurora Mist (IRE)</t>
+          <t>Amerilis</t>
         </is>
       </c>
       <c r="I3" t="n">
         <v>3</v>
       </c>
       <c r="J3" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K3" t="n">
-        <v>63</v>
-      </c>
-      <c r="L3" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="L3" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M3" t="n">
         <v>75.65000000000001</v>
       </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>80.7</v>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>-20</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="4">
@@ -630,11 +636,11 @@
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Dubai Opulence (IRE)</t>
+          <t>Pocket Jacks (IRE)</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -646,18 +652,22 @@
       <c r="K4" t="n">
         <v>53</v>
       </c>
-      <c r="L4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>4.75</v>
+      </c>
       <c r="M4" t="n">
         <v>75.65000000000001</v>
       </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="N4" t="n">
+        <v>71.90000000000001</v>
+      </c>
       <c r="O4" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>-20</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="5">
@@ -684,28 +694,30 @@
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Meriden</t>
+          <t>Coincidental Glory (IRE)</t>
         </is>
       </c>
       <c r="I5" t="n">
         <v>3</v>
       </c>
       <c r="J5" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="K5" t="n">
-        <v>72</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L5" t="n">
+        <v>4.85</v>
+      </c>
       <c r="M5" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>94.8</v>
+        <v>81</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -713,7 +725,7 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -740,30 +752,30 @@
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Amerilis</t>
+          <t>Apothic Red (IRE)</t>
         </is>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K6" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="L6" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>80.7</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -771,7 +783,7 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -798,30 +810,30 @@
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pocket Jacks (IRE)</t>
+          <t>Kilmac Air (IRE)</t>
         </is>
       </c>
       <c r="I7" t="n">
         <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="K7" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="L7" t="n">
-        <v>4.75</v>
+        <v>6.75</v>
       </c>
       <c r="M7" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>71.90000000000001</v>
+        <v>65.8</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -829,7 +841,7 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="8">
@@ -856,30 +868,30 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Coincidental Glory (IRE)</t>
+          <t>Cisterna (IRE)</t>
         </is>
       </c>
       <c r="I8" t="n">
         <v>3</v>
       </c>
       <c r="J8" t="n">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="K8" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="L8" t="n">
-        <v>4.85</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -887,7 +899,7 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -914,30 +926,30 @@
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Apothic Red (IRE)</t>
+          <t>Schoolyard Days (IRE)</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="K9" t="n">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="L9" t="n">
-        <v>5</v>
+        <v>8.75</v>
       </c>
       <c r="M9" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>75.40000000000001</v>
+        <v>58.5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -945,7 +957,7 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="10">
@@ -972,30 +984,30 @@
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kilmac Air (IRE)</t>
+          <t>Caitouna (IRE)</t>
         </is>
       </c>
       <c r="I10" t="n">
         <v>3</v>
       </c>
       <c r="J10" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K10" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="L10" t="n">
-        <v>6.75</v>
+        <v>9.25</v>
       </c>
       <c r="M10" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>69.5</v>
+        <v>63.8</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1003,7 +1015,7 @@
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1030,30 +1042,30 @@
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Cisterna (IRE)</t>
+          <t>Whats It All About (IRE)</t>
         </is>
       </c>
       <c r="I11" t="n">
         <v>3</v>
       </c>
       <c r="J11" t="n">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="K11" t="n">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M11" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>67</v>
+        <v>57.4</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1088,30 +1100,30 @@
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schoolyard Days (IRE)</t>
+          <t>Gonna Be Golden (IRE)</t>
         </is>
       </c>
       <c r="I12" t="n">
         <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="K12" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="L12" t="n">
-        <v>8.75</v>
+        <v>11</v>
       </c>
       <c r="M12" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>58.5</v>
+        <v>59.7</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
@@ -1119,7 +1131,7 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1146,30 +1158,30 @@
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Caitouna (IRE)</t>
+          <t>Dawn Flame</t>
         </is>
       </c>
       <c r="I13" t="n">
         <v>3</v>
       </c>
       <c r="J13" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="K13" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="L13" t="n">
-        <v>9.25</v>
+        <v>13.5</v>
       </c>
       <c r="M13" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>68.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1177,7 +1189,7 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14">
@@ -1204,30 +1216,30 @@
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Whats It All About (IRE)</t>
+          <t>Whistling Jamesie</t>
         </is>
       </c>
       <c r="I14" t="n">
         <v>3</v>
       </c>
       <c r="J14" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="K14" t="n">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="L14" t="n">
-        <v>10</v>
+        <v>13.55</v>
       </c>
       <c r="M14" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>57.4</v>
+        <v>56.2</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1235,7 +1247,7 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1262,30 +1274,30 @@
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Gonna Be Golden (IRE)</t>
+          <t>Wild Berries (IRE)</t>
         </is>
       </c>
       <c r="I15" t="n">
         <v>3</v>
       </c>
       <c r="J15" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="K15" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L15" t="n">
-        <v>11</v>
+        <v>14.55</v>
       </c>
       <c r="M15" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>62.5</v>
+        <v>51.1</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1293,7 +1305,7 @@
         </is>
       </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1320,30 +1332,30 @@
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Dawn Flame</t>
+          <t>Polanco (IRE)</t>
         </is>
       </c>
       <c r="I16" t="n">
         <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="K16" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="L16" t="n">
-        <v>13.5</v>
+        <v>15.3</v>
       </c>
       <c r="M16" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>54.1</v>
+        <v>44.5</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1351,7 +1363,7 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1378,30 +1390,30 @@
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Whistling Jamesie</t>
+          <t>Windsor Lily (IRE)</t>
         </is>
       </c>
       <c r="I17" t="n">
         <v>3</v>
       </c>
       <c r="J17" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K17" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="L17" t="n">
-        <v>13.55</v>
+        <v>17.8</v>
       </c>
       <c r="M17" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>56.2</v>
+        <v>25</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
@@ -1409,7 +1421,7 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18">
@@ -1436,30 +1448,30 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Wild Berries (IRE)</t>
+          <t>Gosford Queen</t>
         </is>
       </c>
       <c r="I18" t="n">
         <v>3</v>
       </c>
       <c r="J18" t="n">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="K18" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="L18" t="n">
-        <v>14.55</v>
+        <v>19.8</v>
       </c>
       <c r="M18" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>56.6</v>
+        <v>23.4</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1467,7 +1479,7 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="19">
@@ -1494,30 +1506,30 @@
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Polanco (IRE)</t>
+          <t>Enthusiastically (IRE)</t>
         </is>
       </c>
       <c r="I19" t="n">
         <v>3</v>
       </c>
       <c r="J19" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K19" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L19" t="n">
-        <v>15.3</v>
+        <v>19.95</v>
       </c>
       <c r="M19" t="n">
         <v>75.65000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>44.5</v>
+        <v>31.6</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1525,7 +1537,7 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1551,40 +1563,24 @@
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
-      <c r="G20" t="n">
-        <v>16</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Windsor Lily (IRE)</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>3</v>
-      </c>
-      <c r="J20" t="n">
-        <v>119</v>
-      </c>
-      <c r="K20" t="n">
-        <v>48</v>
-      </c>
-      <c r="L20" t="n">
-        <v>17.8</v>
-      </c>
-      <c r="M20" t="n">
-        <v>75.65000000000001</v>
-      </c>
-      <c r="N20" t="n">
-        <v>26.9</v>
-      </c>
+          <t>Aurora Mist (IRE)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P20" t="n">
-        <v>-2</v>
-      </c>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1609,40 +1605,24 @@
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
-      <c r="G21" t="n">
-        <v>17</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Gosford Queen</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>123</v>
-      </c>
-      <c r="K21" t="n">
-        <v>53</v>
-      </c>
-      <c r="L21" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="M21" t="n">
-        <v>75.65000000000001</v>
-      </c>
-      <c r="N21" t="n">
-        <v>28.1</v>
-      </c>
+          <t>Dubai Opulence (IRE)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1667,40 +1647,24 @@
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
-      <c r="G22" t="n">
-        <v>18</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Enthusiastically (IRE)</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>3</v>
-      </c>
-      <c r="J22" t="n">
-        <v>127</v>
-      </c>
-      <c r="K22" t="n">
-        <v>57</v>
-      </c>
-      <c r="L22" t="n">
-        <v>19.95</v>
-      </c>
-      <c r="M22" t="n">
-        <v>75.65000000000001</v>
-      </c>
-      <c r="N22" t="n">
-        <v>31.6</v>
-      </c>
+          <t>Boston Max (IRE)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="O22" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P22" t="n">
-        <v>2</v>
-      </c>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2089,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>5.05</v>
+        <v>5.050000000000001</v>
       </c>
       <c r="M29" t="n">
         <v>76.09</v>
@@ -2147,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>5.2</v>
+        <v>5.200000000000001</v>
       </c>
       <c r="M30" t="n">
         <v>76.09</v>
@@ -2431,7 +2395,7 @@
         <v>3</v>
       </c>
       <c r="J35" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K35" t="n">
         <v>0</v>
@@ -2443,7 +2407,7 @@
         <v>76.09</v>
       </c>
       <c r="N35" t="n">
-        <v>52.3</v>
+        <v>52.1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2768,11 +2732,11 @@
       </c>
       <c r="F41" t="inlineStr"/>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Selwyn (IRE)</t>
+          <t>Aix La Chapelle (USA)</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2788,14 +2752,16 @@
       <c r="M41" t="n">
         <v>86.3</v>
       </c>
-      <c r="N41" t="inlineStr"/>
+      <c r="N41" t="n">
+        <v>102</v>
+      </c>
       <c r="O41" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2822,11 +2788,11 @@
       </c>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Aix La Chapelle (USA)</t>
+          <t>Bull Shark (IRE)</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2838,12 +2804,14 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr"/>
+      <c r="L42" t="n">
+        <v>1.5</v>
+      </c>
       <c r="M42" t="n">
         <v>86.3</v>
       </c>
       <c r="N42" t="n">
-        <v>102</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -2878,11 +2846,11 @@
       </c>
       <c r="F43" t="inlineStr"/>
       <c r="G43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Bull Shark (IRE)</t>
+          <t>Giant Sequoia (USA)</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2895,13 +2863,13 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>3.25</v>
       </c>
       <c r="M43" t="n">
         <v>86.3</v>
       </c>
       <c r="N43" t="n">
-        <v>95.90000000000001</v>
+        <v>91</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -2936,11 +2904,11 @@
       </c>
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Giant Sequoia (USA)</t>
+          <t>Breath Of Paradise (IRE)</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2953,13 +2921,13 @@
         <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>3.25</v>
+        <v>11.75</v>
       </c>
       <c r="M44" t="n">
         <v>86.3</v>
       </c>
       <c r="N44" t="n">
-        <v>91</v>
+        <v>60.5</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -2994,11 +2962,11 @@
       </c>
       <c r="F45" t="inlineStr"/>
       <c r="G45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Breath Of Paradise (IRE)</t>
+          <t>Peckedbytheparrott (IRE)</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -3011,13 +2979,13 @@
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>11.75</v>
+        <v>13.5</v>
       </c>
       <c r="M45" t="n">
         <v>86.3</v>
       </c>
       <c r="N45" t="n">
-        <v>60.5</v>
+        <v>57.8</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3052,11 +3020,11 @@
       </c>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Peckedbytheparrott (IRE)</t>
+          <t>To Infinity (FR)</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -3069,13 +3037,13 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="M46" t="n">
         <v>86.3</v>
       </c>
       <c r="N46" t="n">
-        <v>57.8</v>
+        <v>46</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3109,40 +3077,24 @@
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="n">
-        <v>6</v>
-      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>To Infinity (FR)</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>2</v>
-      </c>
-      <c r="J47" t="n">
-        <v>133</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>16</v>
-      </c>
-      <c r="M47" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="N47" t="n">
-        <v>46</v>
-      </c>
+          <t>Selwyn (IRE)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3168,11 +3120,11 @@
       </c>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Nation Blaze (IRE)</t>
+          <t>Celeron</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3188,14 +3140,16 @@
       <c r="M48" t="n">
         <v>73.20999999999999</v>
       </c>
-      <c r="N48" t="inlineStr"/>
+      <c r="N48" t="n">
+        <v>97</v>
+      </c>
       <c r="O48" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P48" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3222,11 +3176,11 @@
       </c>
       <c r="F49" t="inlineStr"/>
       <c r="G49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Celeron</t>
+          <t>One Number (USA)</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3238,12 +3192,14 @@
       <c r="K49" t="n">
         <v>0</v>
       </c>
-      <c r="L49" t="inlineStr"/>
+      <c r="L49" t="n">
+        <v>2</v>
+      </c>
       <c r="M49" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>97</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3278,11 +3234,11 @@
       </c>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>One Number (USA)</t>
+          <t>Tradewinds (IRE)</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3295,13 +3251,13 @@
         <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="M50" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>92.59999999999999</v>
+        <v>91.8</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3336,11 +3292,11 @@
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Tradewinds (IRE)</t>
+          <t>Sirocco Sands (IRE)</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3353,13 +3309,13 @@
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M51" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>91.8</v>
+        <v>90.5</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3394,30 +3350,30 @@
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Sirocco Sands (IRE)</t>
+          <t>Little Miss Muffet (IRE)</t>
         </is>
       </c>
       <c r="I52" t="n">
         <v>2</v>
       </c>
       <c r="J52" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K52" t="n">
         <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>2.1</v>
+        <v>8.1</v>
       </c>
       <c r="M52" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>90.5</v>
+        <v>73</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3425,7 +3381,7 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="53">
@@ -3452,30 +3408,30 @@
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Little Miss Muffet (IRE)</t>
+          <t>La Tache (IRE)</t>
         </is>
       </c>
       <c r="I53" t="n">
         <v>2</v>
       </c>
       <c r="J53" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>8.1</v>
+        <v>8.25</v>
       </c>
       <c r="M53" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>73</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3483,7 +3439,7 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3510,30 +3466,30 @@
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>La Tache (IRE)</t>
+          <t>Gwen (IRE)</t>
         </is>
       </c>
       <c r="I54" t="n">
         <v>2</v>
       </c>
       <c r="J54" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K54" t="n">
         <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>8.25</v>
+        <v>9.5</v>
       </c>
       <c r="M54" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>74.40000000000001</v>
+        <v>69.8</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3541,7 +3497,7 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="55">
@@ -3568,30 +3524,30 @@
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Gwen (IRE)</t>
+          <t>Orchestrating (IRE)</t>
         </is>
       </c>
       <c r="I55" t="n">
         <v>2</v>
       </c>
       <c r="J55" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K55" t="n">
         <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
       <c r="M55" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>69.8</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3599,7 +3555,7 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3626,30 +3582,30 @@
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Orchestrating (IRE)</t>
+          <t>Thatsanotherstory</t>
         </is>
       </c>
       <c r="I56" t="n">
         <v>2</v>
       </c>
       <c r="J56" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>9.6</v>
+        <v>12.85</v>
       </c>
       <c r="M56" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>70.90000000000001</v>
+        <v>55.9</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3657,7 +3613,7 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="57">
@@ -3684,24 +3640,24 @@
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Thatsanotherstory</t>
+          <t>Winnies Wish (IRE)</t>
         </is>
       </c>
       <c r="I57" t="n">
         <v>2</v>
       </c>
       <c r="J57" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>12.85</v>
+        <v>13.6</v>
       </c>
       <c r="M57" t="n">
         <v>73.20999999999999</v>
@@ -3715,7 +3671,7 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="58">
@@ -3742,11 +3698,11 @@
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Winnies Wish (IRE)</t>
+          <t>Tennesspeed (USA)</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3759,13 +3715,13 @@
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>13.6</v>
+        <v>15.35</v>
       </c>
       <c r="M58" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>55.9</v>
+        <v>45</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3773,7 +3729,7 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3800,11 +3756,11 @@
       </c>
       <c r="F59" t="inlineStr"/>
       <c r="G59" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Tennesspeed (USA)</t>
+          <t>Captain James Cook</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3817,13 +3773,13 @@
         <v>0</v>
       </c>
       <c r="L59" t="n">
-        <v>15.35</v>
+        <v>16.6</v>
       </c>
       <c r="M59" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>45</v>
+        <v>42.9</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3858,30 +3814,30 @@
       </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Captain James Cook</t>
+          <t>Dropping Dimes (IRE)</t>
         </is>
       </c>
       <c r="I60" t="n">
         <v>2</v>
       </c>
       <c r="J60" t="n">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K60" t="n">
         <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>16.6</v>
+        <v>18.35</v>
       </c>
       <c r="M60" t="n">
         <v>73.20999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>42.9</v>
+        <v>35.3</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -3915,40 +3871,24 @@
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="n">
-        <v>13</v>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Dropping Dimes (IRE)</t>
-        </is>
-      </c>
-      <c r="I61" t="n">
-        <v>2</v>
-      </c>
-      <c r="J61" t="n">
-        <v>128</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" t="n">
-        <v>18.35</v>
-      </c>
-      <c r="M61" t="n">
-        <v>73.20999999999999</v>
-      </c>
-      <c r="N61" t="n">
-        <v>35.3</v>
-      </c>
+          <t>Nation Blaze (IRE)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4273,7 +4213,7 @@
         <v>3</v>
       </c>
       <c r="J67" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K67" t="n">
         <v>79</v>
@@ -4285,7 +4225,7 @@
         <v>59.04</v>
       </c>
       <c r="N67" t="n">
-        <v>87.40000000000001</v>
+        <v>80.7</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4293,7 +4233,7 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="68">
@@ -4351,7 +4291,7 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4389,19 +4329,19 @@
         <v>3</v>
       </c>
       <c r="J69" t="n">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="K69" t="n">
         <v>78</v>
       </c>
       <c r="L69" t="n">
-        <v>3.13</v>
+        <v>3.129999999999999</v>
       </c>
       <c r="M69" t="n">
         <v>59.04</v>
       </c>
       <c r="N69" t="n">
-        <v>80.8</v>
+        <v>76.3</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4505,7 +4445,7 @@
         <v>3</v>
       </c>
       <c r="J71" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K71" t="n">
         <v>72</v>
@@ -4517,7 +4457,7 @@
         <v>59.04</v>
       </c>
       <c r="N71" t="n">
-        <v>66.5</v>
+        <v>61.2</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4563,7 +4503,7 @@
         <v>3</v>
       </c>
       <c r="J72" t="n">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="K72" t="n">
         <v>73</v>
@@ -4575,7 +4515,7 @@
         <v>59.04</v>
       </c>
       <c r="N72" t="n">
-        <v>65.3</v>
+        <v>60</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4621,19 +4561,19 @@
         <v>3</v>
       </c>
       <c r="J73" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="K73" t="n">
         <v>78</v>
       </c>
       <c r="L73" t="n">
-        <v>8.779999999999999</v>
+        <v>8.780000000000001</v>
       </c>
       <c r="M73" t="n">
         <v>59.04</v>
       </c>
       <c r="N73" t="n">
-        <v>61.3</v>
+        <v>55.7</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -5045,7 +4985,7 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="81">
@@ -5103,7 +5043,7 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="82">
@@ -5141,7 +5081,7 @@
         <v>5</v>
       </c>
       <c r="J82" t="n">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="K82" t="n">
         <v>88</v>
@@ -5153,7 +5093,7 @@
         <v>182.16</v>
       </c>
       <c r="N82" t="n">
-        <v>80.3</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="O82" t="inlineStr">
         <is>
@@ -5161,7 +5101,7 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="83">
@@ -5219,7 +5159,7 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -5257,7 +5197,7 @@
         <v>5</v>
       </c>
       <c r="J84" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K84" t="n">
         <v>98</v>
@@ -5269,7 +5209,7 @@
         <v>182.16</v>
       </c>
       <c r="N84" t="n">
-        <v>86.5</v>
+        <v>83.5</v>
       </c>
       <c r="O84" t="inlineStr">
         <is>
@@ -5277,7 +5217,7 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -5335,7 +5275,7 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -5835,7 +5775,7 @@
         <v>3</v>
       </c>
       <c r="J94" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="K94" t="n">
         <v>56</v>
@@ -5847,7 +5787,7 @@
         <v>157.17</v>
       </c>
       <c r="N94" t="n">
-        <v>77.59999999999999</v>
+        <v>71.5</v>
       </c>
       <c r="O94" t="inlineStr">
         <is>
@@ -5882,34 +5822,36 @@
       </c>
       <c r="F95" t="inlineStr"/>
       <c r="G95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Dynamic Force (IRE)</t>
+          <t>Sommelier</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="J95" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="K95" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="n">
         <v>76.5</v>
       </c>
-      <c r="N95" t="inlineStr"/>
+      <c r="N95" t="n">
+        <v>84.09999999999999</v>
+      </c>
       <c r="O95" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P95" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -5936,34 +5878,38 @@
       </c>
       <c r="F96" t="inlineStr"/>
       <c r="G96" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Hugos Girl (IRE)</t>
+          <t>Irish Rumour (IRE)</t>
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J96" t="n">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="K96" t="n">
-        <v>62</v>
-      </c>
-      <c r="L96" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="L96" t="n">
+        <v>1.75</v>
+      </c>
       <c r="M96" t="n">
         <v>76.5</v>
       </c>
-      <c r="N96" t="inlineStr"/>
+      <c r="N96" t="n">
+        <v>73.3</v>
+      </c>
       <c r="O96" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P96" t="n">
-        <v>-22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -5990,34 +5936,38 @@
       </c>
       <c r="F97" t="inlineStr"/>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Jazzit</t>
+          <t>Hot To Foxtrot (IRE)</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J97" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="K97" t="n">
-        <v>55</v>
-      </c>
-      <c r="L97" t="inlineStr"/>
+        <v>53</v>
+      </c>
+      <c r="L97" t="n">
+        <v>3.5</v>
+      </c>
       <c r="M97" t="n">
         <v>76.5</v>
       </c>
-      <c r="N97" t="inlineStr"/>
+      <c r="N97" t="n">
+        <v>64</v>
+      </c>
       <c r="O97" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P97" t="n">
-        <v>-22</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="98">
@@ -6044,28 +5994,30 @@
       </c>
       <c r="F98" t="inlineStr"/>
       <c r="G98" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sommelier</t>
+          <t>Poweracclaim (IRE)</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J98" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="K98" t="n">
-        <v>72</v>
-      </c>
-      <c r="L98" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="L98" t="n">
+        <v>5.25</v>
+      </c>
       <c r="M98" t="n">
         <v>76.5</v>
       </c>
       <c r="N98" t="n">
-        <v>87.2</v>
+        <v>66.7</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
@@ -6073,7 +6025,7 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="99">
@@ -6100,30 +6052,30 @@
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Irish Rumour (IRE)</t>
+          <t>Eichan San (IRE)</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J99" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K99" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L99" t="n">
-        <v>1.75</v>
+        <v>5.75</v>
       </c>
       <c r="M99" t="n">
         <v>76.5</v>
       </c>
       <c r="N99" t="n">
-        <v>73.3</v>
+        <v>57.7</v>
       </c>
       <c r="O99" t="inlineStr">
         <is>
@@ -6131,7 +6083,7 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="100">
@@ -6158,30 +6110,30 @@
       </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Hot To Foxtrot (IRE)</t>
+          <t>Dandy Land (IRE)</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J100" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="K100" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L100" t="n">
-        <v>3.5</v>
+        <v>6.25</v>
       </c>
       <c r="M100" t="n">
         <v>76.5</v>
       </c>
       <c r="N100" t="n">
-        <v>64</v>
+        <v>55.1</v>
       </c>
       <c r="O100" t="inlineStr">
         <is>
@@ -6189,7 +6141,7 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>-1</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="101">
@@ -6216,30 +6168,30 @@
       </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Poweracclaim (IRE)</t>
+          <t>Jon Riggens (IRE)</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J101" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="K101" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="L101" t="n">
-        <v>5.25</v>
+        <v>6.28</v>
       </c>
       <c r="M101" t="n">
         <v>76.5</v>
       </c>
       <c r="N101" t="n">
-        <v>66.7</v>
+        <v>63.2</v>
       </c>
       <c r="O101" t="inlineStr">
         <is>
@@ -6247,7 +6199,7 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="102">
@@ -6274,30 +6226,30 @@
       </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Eichan San (IRE)</t>
+          <t>Green Icon (FR)</t>
         </is>
       </c>
       <c r="I102" t="n">
         <v>4</v>
       </c>
       <c r="J102" t="n">
-        <v>133</v>
+        <v>119</v>
       </c>
       <c r="K102" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L102" t="n">
-        <v>5.75</v>
+        <v>6.78</v>
       </c>
       <c r="M102" t="n">
         <v>76.5</v>
       </c>
       <c r="N102" t="n">
-        <v>59.6</v>
+        <v>49.7</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -6305,7 +6257,7 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>-3</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="103">
@@ -6332,30 +6284,30 @@
       </c>
       <c r="F103" t="inlineStr"/>
       <c r="G103" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Dandy Land (IRE)</t>
+          <t>Lady Mary Heath (IRE)</t>
         </is>
       </c>
       <c r="I103" t="n">
         <v>4</v>
       </c>
       <c r="J103" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K103" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="L103" t="n">
-        <v>6.25</v>
+        <v>6.93</v>
       </c>
       <c r="M103" t="n">
         <v>76.5</v>
       </c>
       <c r="N103" t="n">
-        <v>55.1</v>
+        <v>57.4</v>
       </c>
       <c r="O103" t="inlineStr">
         <is>
@@ -6363,7 +6315,7 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>-6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="104">
@@ -6390,30 +6342,30 @@
       </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Jon Riggens (IRE)</t>
+          <t>Carrigans Grove (IRE)</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J104" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="K104" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L104" t="n">
-        <v>6.28</v>
+        <v>7.08</v>
       </c>
       <c r="M104" t="n">
         <v>76.5</v>
       </c>
       <c r="N104" t="n">
-        <v>63.2</v>
+        <v>61.8</v>
       </c>
       <c r="O104" t="inlineStr">
         <is>
@@ -6421,7 +6373,7 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -6448,30 +6400,30 @@
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Green Icon (FR)</t>
+          <t>Kitty Bear (IRE)</t>
         </is>
       </c>
       <c r="I105" t="n">
         <v>4</v>
       </c>
       <c r="J105" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="K105" t="n">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L105" t="n">
-        <v>6.78</v>
+        <v>7.13</v>
       </c>
       <c r="M105" t="n">
         <v>76.5</v>
       </c>
       <c r="N105" t="n">
-        <v>57.8</v>
+        <v>57</v>
       </c>
       <c r="O105" t="inlineStr">
         <is>
@@ -6479,7 +6431,7 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>-2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="106">
@@ -6506,30 +6458,30 @@
       </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Lady Mary Heath (IRE)</t>
+          <t>Rosato (IRE)</t>
         </is>
       </c>
       <c r="I106" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J106" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="K106" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="L106" t="n">
-        <v>6.93</v>
+        <v>7.63</v>
       </c>
       <c r="M106" t="n">
         <v>76.5</v>
       </c>
       <c r="N106" t="n">
-        <v>58.7</v>
+        <v>55.6</v>
       </c>
       <c r="O106" t="inlineStr">
         <is>
@@ -6537,7 +6489,7 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -6564,30 +6516,30 @@
       </c>
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Carrigans Grove (IRE)</t>
+          <t>Gegenpressing</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J107" t="n">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="K107" t="n">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="L107" t="n">
-        <v>7.08</v>
+        <v>8.129999999999999</v>
       </c>
       <c r="M107" t="n">
         <v>76.5</v>
       </c>
       <c r="N107" t="n">
-        <v>61.8</v>
+        <v>45.7</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -6595,7 +6547,7 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>4</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="108">
@@ -6622,30 +6574,30 @@
       </c>
       <c r="F108" t="inlineStr"/>
       <c r="G108" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Kitty Bear (IRE)</t>
+          <t>Rappell (IRE)</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J108" t="n">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="K108" t="n">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="L108" t="n">
-        <v>7.13</v>
+        <v>8.879999999999999</v>
       </c>
       <c r="M108" t="n">
         <v>76.5</v>
       </c>
       <c r="N108" t="n">
-        <v>61.6</v>
+        <v>46.1</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -6653,7 +6605,7 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -6680,30 +6632,30 @@
       </c>
       <c r="F109" t="inlineStr"/>
       <c r="G109" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Rosato (IRE)</t>
+          <t>Ukiyo (IRE)</t>
         </is>
       </c>
       <c r="I109" t="n">
         <v>5</v>
       </c>
       <c r="J109" t="n">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="K109" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="L109" t="n">
-        <v>7.63</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M109" t="n">
         <v>76.5</v>
       </c>
       <c r="N109" t="n">
-        <v>55.6</v>
+        <v>41.6</v>
       </c>
       <c r="O109" t="inlineStr">
         <is>
@@ -6711,7 +6663,7 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="110">
@@ -6738,30 +6690,30 @@
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Gegenpressing</t>
+          <t>Angel Of Promise (IRE)</t>
         </is>
       </c>
       <c r="I110" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J110" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="K110" t="n">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="L110" t="n">
-        <v>8.130000000000001</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M110" t="n">
         <v>76.5</v>
       </c>
       <c r="N110" t="n">
-        <v>45.7</v>
+        <v>51.7</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -6769,7 +6721,7 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>-2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="111">
@@ -6796,30 +6748,30 @@
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Rappell (IRE)</t>
+          <t>Shamanka (IRE)</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J111" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K111" t="n">
         <v>62</v>
       </c>
       <c r="L111" t="n">
-        <v>8.880000000000001</v>
+        <v>10.63</v>
       </c>
       <c r="M111" t="n">
         <v>76.5</v>
       </c>
       <c r="N111" t="n">
-        <v>53.8</v>
+        <v>43.8</v>
       </c>
       <c r="O111" t="inlineStr">
         <is>
@@ -6854,30 +6806,30 @@
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Ukiyo (IRE)</t>
+          <t>Prime Sign (IRE)</t>
         </is>
       </c>
       <c r="I112" t="n">
         <v>5</v>
       </c>
       <c r="J112" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="K112" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="L112" t="n">
-        <v>9.380000000000001</v>
+        <v>17.13</v>
       </c>
       <c r="M112" t="n">
         <v>76.5</v>
       </c>
       <c r="N112" t="n">
-        <v>44.5</v>
+        <v>28.3</v>
       </c>
       <c r="O112" t="inlineStr">
         <is>
@@ -6885,7 +6837,7 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -6912,38 +6864,38 @@
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Angel Of Promise (IRE)</t>
+          <t>Salah Belle (IRE)</t>
         </is>
       </c>
       <c r="I113" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J113" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K113" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="L113" t="n">
-        <v>9.880000000000001</v>
+        <v>32.13</v>
       </c>
       <c r="M113" t="n">
         <v>76.5</v>
       </c>
       <c r="N113" t="n">
-        <v>51.7</v>
+        <v>27.4</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P113" t="n">
-        <v>2</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="114">
@@ -6970,38 +6922,38 @@
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Shamanka (IRE)</t>
+          <t>Four Blondes (IRE)</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J114" t="n">
-        <v>132</v>
+        <v>142</v>
       </c>
       <c r="K114" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="L114" t="n">
-        <v>10.63</v>
+        <v>35.63</v>
       </c>
       <c r="M114" t="n">
         <v>76.5</v>
       </c>
       <c r="N114" t="n">
-        <v>44</v>
+        <v>27.4</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="115">
@@ -7027,40 +6979,24 @@
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
-      <c r="G115" t="n">
-        <v>18</v>
-      </c>
+      <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Prime Sign (IRE)</t>
-        </is>
-      </c>
-      <c r="I115" t="n">
-        <v>5</v>
-      </c>
-      <c r="J115" t="n">
-        <v>130</v>
-      </c>
-      <c r="K115" t="n">
-        <v>60</v>
-      </c>
-      <c r="L115" t="n">
-        <v>17.13</v>
-      </c>
-      <c r="M115" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="N115" t="n">
-        <v>28.3</v>
-      </c>
+          <t>Jazzit</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
+      <c r="P115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7085,40 +7021,24 @@
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
-      <c r="G116" t="n">
-        <v>19</v>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Salah Belle (IRE)</t>
-        </is>
-      </c>
-      <c r="I116" t="n">
-        <v>5</v>
-      </c>
-      <c r="J116" t="n">
-        <v>129</v>
-      </c>
-      <c r="K116" t="n">
-        <v>59</v>
-      </c>
-      <c r="L116" t="n">
-        <v>32.13</v>
-      </c>
-      <c r="M116" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="N116" t="n">
-        <v>27.4</v>
-      </c>
+          <t>Hugos Girl (IRE)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P116" t="n">
-        <v>-0.5</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7143,40 +7063,24 @@
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
-      <c r="G117" t="n">
-        <v>20</v>
-      </c>
+      <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Four Blondes (IRE)</t>
-        </is>
-      </c>
-      <c r="I117" t="n">
-        <v>5</v>
-      </c>
-      <c r="J117" t="n">
-        <v>142</v>
-      </c>
-      <c r="K117" t="n">
-        <v>72</v>
-      </c>
-      <c r="L117" t="n">
-        <v>35.63</v>
-      </c>
-      <c r="M117" t="n">
-        <v>76.5</v>
-      </c>
-      <c r="N117" t="n">
-        <v>27.4</v>
-      </c>
+          <t>Dynamic Force (IRE)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P117" t="n">
-        <v>0.5</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7333,7 +7237,7 @@
         <v>2</v>
       </c>
       <c r="J120" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K120" t="n">
         <v>0</v>
@@ -7345,7 +7249,7 @@
         <v>75.5</v>
       </c>
       <c r="N120" t="n">
-        <v>67</v>
+        <v>64.8</v>
       </c>
       <c r="O120" t="inlineStr">
         <is>
@@ -7353,7 +7257,7 @@
         </is>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="121">
@@ -7413,7 +7317,7 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="122">
@@ -7473,7 +7377,7 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -8177,7 +8081,7 @@
         <v>0</v>
       </c>
       <c r="L134" t="n">
-        <v>4.399999999999999</v>
+        <v>4.4</v>
       </c>
       <c r="M134" t="n">
         <v>61.34</v>
@@ -8237,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="L135" t="n">
-        <v>4.899999999999999</v>
+        <v>4.9</v>
       </c>
       <c r="M135" t="n">
         <v>61.34</v>
@@ -8351,7 +8255,7 @@
         <v>2</v>
       </c>
       <c r="J137" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K137" t="n">
         <v>0</v>
@@ -8363,7 +8267,7 @@
         <v>61.34</v>
       </c>
       <c r="N137" t="n">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -8477,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="L139" t="n">
-        <v>7.2</v>
+        <v>7.199999999999999</v>
       </c>
       <c r="M139" t="n">
         <v>61.34</v>
@@ -8520,34 +8424,36 @@
         <v>5</v>
       </c>
       <c r="G140" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bami (IRE)</t>
+          <t>Lillie Margot</t>
         </is>
       </c>
       <c r="I140" t="n">
         <v>3</v>
       </c>
       <c r="J140" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K140" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" t="n">
         <v>106.81</v>
       </c>
-      <c r="N140" t="inlineStr"/>
+      <c r="N140" t="n">
+        <v>74.7</v>
+      </c>
       <c r="O140" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P140" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -8576,28 +8482,30 @@
         <v>5</v>
       </c>
       <c r="G141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Lillie Margot</t>
+          <t>Safe Harbor</t>
         </is>
       </c>
       <c r="I141" t="n">
         <v>3</v>
       </c>
       <c r="J141" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K141" t="n">
-        <v>68</v>
-      </c>
-      <c r="L141" t="inlineStr"/>
+        <v>67</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.75</v>
+      </c>
       <c r="M141" t="n">
         <v>106.81</v>
       </c>
       <c r="N141" t="n">
-        <v>74.7</v>
+        <v>72.3</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
@@ -8634,30 +8542,30 @@
         <v>5</v>
       </c>
       <c r="G142" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Safe Harbor</t>
+          <t>Jamie Sommers (IRE)</t>
         </is>
       </c>
       <c r="I142" t="n">
         <v>3</v>
       </c>
       <c r="J142" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K142" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L142" t="n">
-        <v>0.75</v>
+        <v>5.5</v>
       </c>
       <c r="M142" t="n">
         <v>106.81</v>
       </c>
       <c r="N142" t="n">
-        <v>72.3</v>
+        <v>60.6</v>
       </c>
       <c r="O142" t="inlineStr">
         <is>
@@ -8665,7 +8573,7 @@
         </is>
       </c>
       <c r="P142" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="143">
@@ -8694,30 +8602,30 @@
         <v>5</v>
       </c>
       <c r="G143" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Jamie Sommers (IRE)</t>
+          <t>Glasgow Kiss</t>
         </is>
       </c>
       <c r="I143" t="n">
         <v>3</v>
       </c>
       <c r="J143" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="K143" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L143" t="n">
-        <v>5.5</v>
+        <v>5.55</v>
       </c>
       <c r="M143" t="n">
         <v>106.81</v>
       </c>
       <c r="N143" t="n">
-        <v>60.6</v>
+        <v>58.2</v>
       </c>
       <c r="O143" t="inlineStr">
         <is>
@@ -8754,30 +8662,30 @@
         <v>5</v>
       </c>
       <c r="G144" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Glasgow Kiss</t>
+          <t>Mimis Magic</t>
         </is>
       </c>
       <c r="I144" t="n">
         <v>3</v>
       </c>
       <c r="J144" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K144" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="L144" t="n">
-        <v>5.55</v>
+        <v>5.6</v>
       </c>
       <c r="M144" t="n">
         <v>106.81</v>
       </c>
       <c r="N144" t="n">
-        <v>58.2</v>
+        <v>60.7</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>
@@ -8785,7 +8693,7 @@
         </is>
       </c>
       <c r="P144" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="145">
@@ -8814,30 +8722,30 @@
         <v>5</v>
       </c>
       <c r="G145" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Mimis Magic</t>
+          <t>Vitality (IRE)</t>
         </is>
       </c>
       <c r="I145" t="n">
         <v>3</v>
       </c>
       <c r="J145" t="n">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="K145" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L145" t="n">
-        <v>5.6</v>
+        <v>10.35</v>
       </c>
       <c r="M145" t="n">
         <v>106.81</v>
       </c>
       <c r="N145" t="n">
-        <v>60.7</v>
+        <v>50.3</v>
       </c>
       <c r="O145" t="inlineStr">
         <is>
@@ -8845,7 +8753,7 @@
         </is>
       </c>
       <c r="P145" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -8874,30 +8782,30 @@
         <v>5</v>
       </c>
       <c r="G146" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Vitality (IRE)</t>
+          <t>Laughterintherain (FR)</t>
         </is>
       </c>
       <c r="I146" t="n">
         <v>3</v>
       </c>
       <c r="J146" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K146" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L146" t="n">
-        <v>10.35</v>
+        <v>10.5</v>
       </c>
       <c r="M146" t="n">
         <v>106.81</v>
       </c>
       <c r="N146" t="n">
-        <v>51.3</v>
+        <v>49.1</v>
       </c>
       <c r="O146" t="inlineStr">
         <is>
@@ -8934,30 +8842,30 @@
         <v>5</v>
       </c>
       <c r="G147" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Laughterintherain (FR)</t>
+          <t>Mayfair Market</t>
         </is>
       </c>
       <c r="I147" t="n">
         <v>3</v>
       </c>
       <c r="J147" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K147" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L147" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="M147" t="n">
         <v>106.81</v>
       </c>
       <c r="N147" t="n">
-        <v>49.1</v>
+        <v>45.1</v>
       </c>
       <c r="O147" t="inlineStr">
         <is>
@@ -8994,30 +8902,30 @@
         <v>5</v>
       </c>
       <c r="G148" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Mayfair Market</t>
+          <t>Morningtoncrescent (IRE)</t>
         </is>
       </c>
       <c r="I148" t="n">
         <v>3</v>
       </c>
       <c r="J148" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K148" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L148" t="n">
-        <v>11.5</v>
+        <v>18.5</v>
       </c>
       <c r="M148" t="n">
         <v>106.81</v>
       </c>
       <c r="N148" t="n">
-        <v>45.1</v>
+        <v>31.2</v>
       </c>
       <c r="O148" t="inlineStr">
         <is>
@@ -9054,30 +8962,30 @@
         <v>5</v>
       </c>
       <c r="G149" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Morningtoncrescent (IRE)</t>
+          <t>Katalyst</t>
         </is>
       </c>
       <c r="I149" t="n">
         <v>3</v>
       </c>
       <c r="J149" t="n">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="K149" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="L149" t="n">
-        <v>18.5</v>
+        <v>19.25</v>
       </c>
       <c r="M149" t="n">
         <v>106.81</v>
       </c>
       <c r="N149" t="n">
-        <v>31.2</v>
+        <v>24.2</v>
       </c>
       <c r="O149" t="inlineStr">
         <is>
@@ -9113,40 +9021,24 @@
       <c r="F150" t="n">
         <v>5</v>
       </c>
-      <c r="G150" t="n">
-        <v>10</v>
-      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Katalyst</t>
-        </is>
-      </c>
-      <c r="I150" t="n">
-        <v>3</v>
-      </c>
-      <c r="J150" t="n">
-        <v>128</v>
-      </c>
-      <c r="K150" t="n">
-        <v>63</v>
-      </c>
-      <c r="L150" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="M150" t="n">
-        <v>106.81</v>
-      </c>
-      <c r="N150" t="n">
-        <v>24.2</v>
-      </c>
+          <t>Bami (IRE)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P150" t="n">
-        <v>0</v>
-      </c>
+      <c r="P150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9483,19 +9375,19 @@
         <v>4</v>
       </c>
       <c r="J156" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="K156" t="n">
         <v>72</v>
       </c>
       <c r="L156" t="n">
-        <v>4.95</v>
+        <v>4.949999999999999</v>
       </c>
       <c r="M156" t="n">
         <v>132.1</v>
       </c>
       <c r="N156" t="n">
-        <v>65.90000000000001</v>
+        <v>62.2</v>
       </c>
       <c r="O156" t="inlineStr">
         <is>
@@ -9772,34 +9664,36 @@
         <v>4</v>
       </c>
       <c r="G161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Mr Bollinger (USA)</t>
+          <t>Barbury Boy</t>
         </is>
       </c>
       <c r="I161" t="n">
         <v>3</v>
       </c>
       <c r="J161" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="K161" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" t="n">
         <v>135.52</v>
       </c>
-      <c r="N161" t="inlineStr"/>
+      <c r="N161" t="n">
+        <v>64.90000000000001</v>
+      </c>
       <c r="O161" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P161" t="n">
-        <v>-7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="162">
@@ -9828,28 +9722,30 @@
         <v>4</v>
       </c>
       <c r="G162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Barbury Boy</t>
+          <t>Gatehouse (IRE)</t>
         </is>
       </c>
       <c r="I162" t="n">
         <v>3</v>
       </c>
       <c r="J162" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="K162" t="n">
-        <v>69</v>
-      </c>
-      <c r="L162" t="inlineStr"/>
+        <v>81</v>
+      </c>
+      <c r="L162" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M162" t="n">
         <v>135.52</v>
       </c>
       <c r="N162" t="n">
-        <v>64.90000000000001</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="O162" t="inlineStr">
         <is>
@@ -9857,7 +9753,7 @@
         </is>
       </c>
       <c r="P162" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163">
@@ -9886,30 +9782,30 @@
         <v>4</v>
       </c>
       <c r="G163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Gatehouse (IRE)</t>
+          <t>Unchartedterritory (IRE)</t>
         </is>
       </c>
       <c r="I163" t="n">
         <v>3</v>
       </c>
       <c r="J163" t="n">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="K163" t="n">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="L163" t="n">
-        <v>0.15</v>
+        <v>3.65</v>
       </c>
       <c r="M163" t="n">
         <v>135.52</v>
       </c>
       <c r="N163" t="n">
-        <v>72.59999999999999</v>
+        <v>57.7</v>
       </c>
       <c r="O163" t="inlineStr">
         <is>
@@ -9917,7 +9813,7 @@
         </is>
       </c>
       <c r="P163" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="164">
@@ -9946,30 +9842,30 @@
         <v>4</v>
       </c>
       <c r="G164" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Unchartedterritory (IRE)</t>
+          <t>Midnight Rodeo (IRE)</t>
         </is>
       </c>
       <c r="I164" t="n">
         <v>3</v>
       </c>
       <c r="J164" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="K164" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="L164" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="M164" t="n">
         <v>135.52</v>
       </c>
       <c r="N164" t="n">
-        <v>57.7</v>
+        <v>63</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
@@ -9977,7 +9873,7 @@
         </is>
       </c>
       <c r="P164" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="165">
@@ -10006,30 +9902,30 @@
         <v>4</v>
       </c>
       <c r="G165" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Midnight Rodeo (IRE)</t>
+          <t>Mudita (IRE)</t>
         </is>
       </c>
       <c r="I165" t="n">
         <v>3</v>
       </c>
       <c r="J165" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K165" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="L165" t="n">
-        <v>4.4</v>
+        <v>5.15</v>
       </c>
       <c r="M165" t="n">
         <v>135.52</v>
       </c>
       <c r="N165" t="n">
-        <v>63</v>
+        <v>57.1</v>
       </c>
       <c r="O165" t="inlineStr">
         <is>
@@ -10037,7 +9933,7 @@
         </is>
       </c>
       <c r="P165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -10066,11 +9962,11 @@
         <v>4</v>
       </c>
       <c r="G166" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Mudita (IRE)</t>
+          <t>That Darn Cantor</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -10083,13 +9979,13 @@
         <v>72</v>
       </c>
       <c r="L166" t="n">
-        <v>5.15</v>
+        <v>16.15</v>
       </c>
       <c r="M166" t="n">
         <v>135.52</v>
       </c>
       <c r="N166" t="n">
-        <v>57.1</v>
+        <v>32.7</v>
       </c>
       <c r="O166" t="inlineStr">
         <is>
@@ -10125,40 +10021,24 @@
       <c r="F167" t="n">
         <v>4</v>
       </c>
-      <c r="G167" t="n">
-        <v>6</v>
-      </c>
+      <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>That Darn Cantor</t>
-        </is>
-      </c>
-      <c r="I167" t="n">
-        <v>3</v>
-      </c>
-      <c r="J167" t="n">
-        <v>127</v>
-      </c>
-      <c r="K167" t="n">
-        <v>72</v>
-      </c>
-      <c r="L167" t="n">
-        <v>16.15</v>
-      </c>
-      <c r="M167" t="n">
-        <v>135.52</v>
-      </c>
-      <c r="N167" t="n">
-        <v>32.7</v>
-      </c>
+          <t>Mr Bollinger (USA)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="O167" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P167" t="n">
-        <v>0</v>
-      </c>
+      <c r="P167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10186,34 +10066,36 @@
         <v>6</v>
       </c>
       <c r="G168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>My Boy Jack</t>
+          <t>Court Of Session</t>
         </is>
       </c>
       <c r="I168" t="n">
         <v>7</v>
       </c>
       <c r="J168" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="K168" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="n">
         <v>75.5</v>
       </c>
-      <c r="N168" t="inlineStr"/>
+      <c r="N168" t="n">
+        <v>62.3</v>
+      </c>
       <c r="O168" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P168" t="n">
-        <v>-11</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="169">
@@ -10242,34 +10124,38 @@
         <v>6</v>
       </c>
       <c r="G169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Alafdhal (IRE)</t>
+          <t>Hint Of The Jungle (IRE)</t>
         </is>
       </c>
       <c r="I169" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="J169" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="K169" t="n">
-        <v>58</v>
-      </c>
-      <c r="L169" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L169" t="n">
+        <v>1.25</v>
+      </c>
       <c r="M169" t="n">
         <v>75.5</v>
       </c>
-      <c r="N169" t="inlineStr"/>
+      <c r="N169" t="n">
+        <v>62.7</v>
+      </c>
       <c r="O169" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P169" t="n">
-        <v>-11</v>
+        <v>1</v>
       </c>
     </row>
     <row r="170">
@@ -10298,34 +10184,38 @@
         <v>6</v>
       </c>
       <c r="G170" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Jake Loves Laura</t>
+          <t>Ishe Worth Agamble</t>
         </is>
       </c>
       <c r="I170" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J170" t="n">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="K170" t="n">
-        <v>47</v>
-      </c>
-      <c r="L170" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="L170" t="n">
+        <v>1.35</v>
+      </c>
       <c r="M170" t="n">
         <v>75.5</v>
       </c>
-      <c r="N170" t="inlineStr"/>
+      <c r="N170" t="n">
+        <v>62</v>
+      </c>
       <c r="O170" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P170" t="n">
-        <v>-11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="171">
@@ -10354,28 +10244,30 @@
         <v>6</v>
       </c>
       <c r="G171" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Court Of Session</t>
+          <t>Run This Way</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J171" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K171" t="n">
-        <v>55</v>
-      </c>
-      <c r="L171" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="L171" t="n">
+        <v>1.4</v>
+      </c>
       <c r="M171" t="n">
         <v>75.5</v>
       </c>
       <c r="N171" t="n">
-        <v>62.3</v>
+        <v>59.3</v>
       </c>
       <c r="O171" t="inlineStr">
         <is>
@@ -10383,7 +10275,7 @@
         </is>
       </c>
       <c r="P171" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -10412,15 +10304,15 @@
         <v>6</v>
       </c>
       <c r="G172" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Hint Of The Jungle (IRE)</t>
+          <t>May Encounter</t>
         </is>
       </c>
       <c r="I172" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J172" t="n">
         <v>135</v>
@@ -10429,13 +10321,13 @@
         <v>60</v>
       </c>
       <c r="L172" t="n">
-        <v>1.25</v>
+        <v>2.65</v>
       </c>
       <c r="M172" t="n">
         <v>75.5</v>
       </c>
       <c r="N172" t="n">
-        <v>62.7</v>
+        <v>58</v>
       </c>
       <c r="O172" t="inlineStr">
         <is>
@@ -10443,7 +10335,7 @@
         </is>
       </c>
       <c r="P172" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173">
@@ -10472,30 +10364,30 @@
         <v>6</v>
       </c>
       <c r="G173" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Ishe Worth Agamble</t>
+          <t>Rinky Tinky Tinky</t>
         </is>
       </c>
       <c r="I173" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J173" t="n">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="K173" t="n">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="L173" t="n">
-        <v>1.35</v>
+        <v>3.9</v>
       </c>
       <c r="M173" t="n">
         <v>75.5</v>
       </c>
       <c r="N173" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="O173" t="inlineStr">
         <is>
@@ -10503,7 +10395,7 @@
         </is>
       </c>
       <c r="P173" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="174">
@@ -10532,30 +10424,30 @@
         <v>6</v>
       </c>
       <c r="G174" t="n">
+        <v>7</v>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Fancy Dancer</t>
+        </is>
+      </c>
+      <c r="I174" t="n">
         <v>4</v>
       </c>
-      <c r="H174" t="inlineStr">
-        <is>
-          <t>Run This Way</t>
-        </is>
-      </c>
-      <c r="I174" t="n">
-        <v>8</v>
-      </c>
       <c r="J174" t="n">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="K174" t="n">
         <v>58</v>
       </c>
       <c r="L174" t="n">
-        <v>1.4</v>
+        <v>5.9</v>
       </c>
       <c r="M174" t="n">
         <v>75.5</v>
       </c>
       <c r="N174" t="n">
-        <v>59.3</v>
+        <v>42.6</v>
       </c>
       <c r="O174" t="inlineStr">
         <is>
@@ -10563,7 +10455,7 @@
         </is>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -10592,30 +10484,30 @@
         <v>6</v>
       </c>
       <c r="G175" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>May Encounter</t>
+          <t>Surprise Again (IRE)</t>
         </is>
       </c>
       <c r="I175" t="n">
         <v>4</v>
       </c>
       <c r="J175" t="n">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="K175" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="L175" t="n">
-        <v>2.65</v>
+        <v>10.9</v>
       </c>
       <c r="M175" t="n">
         <v>75.5</v>
       </c>
       <c r="N175" t="n">
-        <v>58</v>
+        <v>14.7</v>
       </c>
       <c r="O175" t="inlineStr">
         <is>
@@ -10652,38 +10544,38 @@
         <v>6</v>
       </c>
       <c r="G176" t="n">
+        <v>9</v>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Tilsworth Turf</t>
+        </is>
+      </c>
+      <c r="I176" t="n">
         <v>6</v>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Rinky Tinky Tinky</t>
-        </is>
-      </c>
-      <c r="I176" t="n">
-        <v>4</v>
-      </c>
       <c r="J176" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="K176" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="L176" t="n">
-        <v>3.9</v>
+        <v>23.9</v>
       </c>
       <c r="M176" t="n">
         <v>75.5</v>
       </c>
       <c r="N176" t="n">
-        <v>42</v>
+        <v>-3.6</v>
       </c>
       <c r="O176" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>low</t>
         </is>
       </c>
       <c r="P176" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -10711,40 +10603,24 @@
       <c r="F177" t="n">
         <v>6</v>
       </c>
-      <c r="G177" t="n">
-        <v>7</v>
-      </c>
+      <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Fancy Dancer</t>
-        </is>
-      </c>
-      <c r="I177" t="n">
-        <v>4</v>
-      </c>
-      <c r="J177" t="n">
-        <v>133</v>
-      </c>
-      <c r="K177" t="n">
-        <v>58</v>
-      </c>
-      <c r="L177" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="M177" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="N177" t="n">
-        <v>44.7</v>
-      </c>
+          <t>Jake Loves Laura</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr"/>
+      <c r="J177" t="inlineStr"/>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P177" t="n">
-        <v>1</v>
-      </c>
+      <c r="P177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -10771,40 +10647,24 @@
       <c r="F178" t="n">
         <v>6</v>
       </c>
-      <c r="G178" t="n">
-        <v>8</v>
-      </c>
+      <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Surprise Again (IRE)</t>
-        </is>
-      </c>
-      <c r="I178" t="n">
-        <v>4</v>
-      </c>
-      <c r="J178" t="n">
-        <v>121</v>
-      </c>
-      <c r="K178" t="n">
-        <v>46</v>
-      </c>
-      <c r="L178" t="n">
-        <v>10.9</v>
-      </c>
-      <c r="M178" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="N178" t="n">
-        <v>20.6</v>
-      </c>
+          <t>My Boy Jack</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr"/>
+      <c r="J178" t="inlineStr"/>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P178" t="n">
-        <v>0</v>
-      </c>
+      <c r="P178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -10831,40 +10691,24 @@
       <c r="F179" t="n">
         <v>6</v>
       </c>
-      <c r="G179" t="n">
-        <v>9</v>
-      </c>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Tilsworth Turf</t>
-        </is>
-      </c>
-      <c r="I179" t="n">
-        <v>6</v>
-      </c>
-      <c r="J179" t="n">
-        <v>121</v>
-      </c>
-      <c r="K179" t="n">
-        <v>46</v>
-      </c>
-      <c r="L179" t="n">
-        <v>23.9</v>
-      </c>
-      <c r="M179" t="n">
-        <v>75.5</v>
-      </c>
-      <c r="N179" t="n">
-        <v>-3.6</v>
-      </c>
+          <t>Alafdhal (IRE)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr"/>
+      <c r="J179" t="inlineStr"/>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="P179" t="n">
-        <v>0</v>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11548,34 +11392,36 @@
         <v>5</v>
       </c>
       <c r="G191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Amidst The Chaos (IRE)</t>
+          <t>Donna Nook</t>
         </is>
       </c>
       <c r="I191" t="n">
         <v>4</v>
       </c>
       <c r="J191" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K191" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="L191" t="inlineStr"/>
       <c r="M191" t="n">
         <v>98.95999999999999</v>
       </c>
-      <c r="N191" t="inlineStr"/>
+      <c r="N191" t="n">
+        <v>82.09999999999999</v>
+      </c>
       <c r="O191" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P191" t="n">
-        <v>-13.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -11604,34 +11450,38 @@
         <v>5</v>
       </c>
       <c r="G192" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Yafaarr (IRE)</t>
+          <t>Jesmond Dawn (IRE)</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J192" t="n">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K192" t="n">
-        <v>62</v>
-      </c>
-      <c r="L192" t="inlineStr"/>
+        <v>63</v>
+      </c>
+      <c r="L192" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M192" t="n">
         <v>98.95999999999999</v>
       </c>
-      <c r="N192" t="inlineStr"/>
+      <c r="N192" t="n">
+        <v>74.90000000000001</v>
+      </c>
       <c r="O192" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P192" t="n">
-        <v>-13.5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="193">
@@ -11660,28 +11510,30 @@
         <v>5</v>
       </c>
       <c r="G193" t="n">
+        <v>3</v>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Barley (IRE)</t>
+        </is>
+      </c>
+      <c r="I193" t="n">
+        <v>7</v>
+      </c>
+      <c r="J193" t="n">
+        <v>131</v>
+      </c>
+      <c r="K193" t="n">
+        <v>66</v>
+      </c>
+      <c r="L193" t="n">
         <v>1</v>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>Donna Nook</t>
-        </is>
-      </c>
-      <c r="I193" t="n">
-        <v>4</v>
-      </c>
-      <c r="J193" t="n">
-        <v>135</v>
-      </c>
-      <c r="K193" t="n">
-        <v>70</v>
-      </c>
-      <c r="L193" t="inlineStr"/>
       <c r="M193" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N193" t="n">
-        <v>82.09999999999999</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="O193" t="inlineStr">
         <is>
@@ -11689,7 +11541,7 @@
         </is>
       </c>
       <c r="P193" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="194">
@@ -11718,30 +11570,30 @@
         <v>5</v>
       </c>
       <c r="G194" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Jesmond Dawn (IRE)</t>
+          <t>Avatar Jet (IRE)</t>
         </is>
       </c>
       <c r="I194" t="n">
         <v>5</v>
       </c>
       <c r="J194" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="K194" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="L194" t="n">
-        <v>0.5</v>
+        <v>2.25</v>
       </c>
       <c r="M194" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N194" t="n">
-        <v>74.90000000000001</v>
+        <v>68</v>
       </c>
       <c r="O194" t="inlineStr">
         <is>
@@ -11778,30 +11630,30 @@
         <v>5</v>
       </c>
       <c r="G195" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Barley (IRE)</t>
+          <t>Perfidia (IRE)</t>
         </is>
       </c>
       <c r="I195" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J195" t="n">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="K195" t="n">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="L195" t="n">
-        <v>1</v>
+        <v>2.4</v>
       </c>
       <c r="M195" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N195" t="n">
-        <v>76.40000000000001</v>
+        <v>61.4</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
@@ -11809,7 +11661,7 @@
         </is>
       </c>
       <c r="P195" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="196">
@@ -11838,11 +11690,11 @@
         <v>5</v>
       </c>
       <c r="G196" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Avatar Jet (IRE)</t>
+          <t>Havana Touch</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -11855,13 +11707,13 @@
         <v>67</v>
       </c>
       <c r="L196" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="M196" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N196" t="n">
-        <v>74.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="O196" t="inlineStr">
         <is>
@@ -11869,7 +11721,7 @@
         </is>
       </c>
       <c r="P196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -11898,30 +11750,30 @@
         <v>5</v>
       </c>
       <c r="G197" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Perfidia (IRE)</t>
+          <t>The New Bay Pearl</t>
         </is>
       </c>
       <c r="I197" t="n">
         <v>4</v>
       </c>
       <c r="J197" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K197" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="L197" t="n">
-        <v>2.4</v>
+        <v>4.800000000000001</v>
       </c>
       <c r="M197" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N197" t="n">
-        <v>65</v>
+        <v>58.1</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
@@ -11929,7 +11781,7 @@
         </is>
       </c>
       <c r="P197" t="n">
-        <v>-2</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="198">
@@ -11958,30 +11810,30 @@
         <v>5</v>
       </c>
       <c r="G198" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Havana Touch</t>
+          <t>Eeetee (IRE)</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J198" t="n">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="K198" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="L198" t="n">
-        <v>2.55</v>
+        <v>4.95</v>
       </c>
       <c r="M198" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N198" t="n">
-        <v>72.7</v>
+        <v>62.8</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
@@ -12018,30 +11870,30 @@
         <v>5</v>
       </c>
       <c r="G199" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>The New Bay Pearl</t>
+          <t>Kiss Me My Love (IRE)</t>
         </is>
       </c>
       <c r="I199" t="n">
         <v>4</v>
       </c>
       <c r="J199" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="K199" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="L199" t="n">
-        <v>4.8</v>
+        <v>5.7</v>
       </c>
       <c r="M199" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N199" t="n">
-        <v>64</v>
+        <v>63.7</v>
       </c>
       <c r="O199" t="inlineStr">
         <is>
@@ -12049,7 +11901,7 @@
         </is>
       </c>
       <c r="P199" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="200">
@@ -12078,30 +11930,30 @@
         <v>5</v>
       </c>
       <c r="G200" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Eeetee (IRE)</t>
+          <t>The Childe Of Hale</t>
         </is>
       </c>
       <c r="I200" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J200" t="n">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="K200" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="L200" t="n">
-        <v>4.95</v>
+        <v>8.950000000000001</v>
       </c>
       <c r="M200" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N200" t="n">
-        <v>67</v>
+        <v>60.5</v>
       </c>
       <c r="O200" t="inlineStr">
         <is>
@@ -12109,7 +11961,7 @@
         </is>
       </c>
       <c r="P200" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="201">
@@ -12138,30 +11990,30 @@
         <v>5</v>
       </c>
       <c r="G201" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Kiss Me My Love (IRE)</t>
+          <t>Superfortress (IRE)</t>
         </is>
       </c>
       <c r="I201" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J201" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="K201" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="L201" t="n">
-        <v>5.7</v>
+        <v>9.1</v>
       </c>
       <c r="M201" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N201" t="n">
-        <v>63.7</v>
+        <v>61.2</v>
       </c>
       <c r="O201" t="inlineStr">
         <is>
@@ -12169,7 +12021,7 @@
         </is>
       </c>
       <c r="P201" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="202">
@@ -12198,30 +12050,30 @@
         <v>5</v>
       </c>
       <c r="G202" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>The Childe Of Hale</t>
+          <t>Travis</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J202" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="K202" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="L202" t="n">
-        <v>8.949999999999999</v>
+        <v>17.6</v>
       </c>
       <c r="M202" t="n">
         <v>98.95999999999999</v>
       </c>
       <c r="N202" t="n">
-        <v>60.5</v>
+        <v>30.5</v>
       </c>
       <c r="O202" t="inlineStr">
         <is>
@@ -12229,7 +12081,7 @@
         </is>
       </c>
       <c r="P202" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -12257,40 +12109,24 @@
       <c r="F203" t="n">
         <v>5</v>
       </c>
-      <c r="G203" t="n">
-        <v>11</v>
-      </c>
+      <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Superfortress (IRE)</t>
-        </is>
-      </c>
-      <c r="I203" t="n">
-        <v>5</v>
-      </c>
-      <c r="J203" t="n">
-        <v>135</v>
-      </c>
-      <c r="K203" t="n">
-        <v>70</v>
-      </c>
-      <c r="L203" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="M203" t="n">
-        <v>98.95999999999999</v>
-      </c>
-      <c r="N203" t="n">
-        <v>61.2</v>
-      </c>
+          <t>Amidst The Chaos (IRE)</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
+      <c r="M203" t="inlineStr"/>
+      <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P203" t="n">
-        <v>1</v>
-      </c>
+      <c r="P203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12317,40 +12153,24 @@
       <c r="F204" t="n">
         <v>5</v>
       </c>
-      <c r="G204" t="n">
-        <v>12</v>
-      </c>
+      <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Travis</t>
-        </is>
-      </c>
-      <c r="I204" t="n">
-        <v>5</v>
-      </c>
-      <c r="J204" t="n">
-        <v>126</v>
-      </c>
-      <c r="K204" t="n">
-        <v>61</v>
-      </c>
-      <c r="L204" t="n">
-        <v>17.6</v>
-      </c>
-      <c r="M204" t="n">
-        <v>98.95999999999999</v>
-      </c>
-      <c r="N204" t="n">
-        <v>30.5</v>
-      </c>
+          <t>Yafaarr (IRE)</t>
+        </is>
+      </c>
+      <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
+      <c r="M204" t="inlineStr"/>
+      <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P204" t="n">
-        <v>0</v>
-      </c>
+      <c r="P204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12378,34 +12198,36 @@
         <v>5</v>
       </c>
       <c r="G205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Raft Up (IRE)</t>
+          <t>Glory Hyde (IRE)</t>
         </is>
       </c>
       <c r="I205" t="n">
         <v>5</v>
       </c>
       <c r="J205" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="K205" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="L205" t="inlineStr"/>
       <c r="M205" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="N205" t="inlineStr"/>
+      <c r="N205" t="n">
+        <v>79.8</v>
+      </c>
       <c r="O205" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P205" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="206">
@@ -12434,34 +12256,38 @@
         <v>5</v>
       </c>
       <c r="G206" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Blind Beggar (IRE)</t>
+          <t>Magic Boy (GER)</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="J206" t="n">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K206" t="n">
-        <v>73</v>
-      </c>
-      <c r="L206" t="inlineStr"/>
+        <v>72</v>
+      </c>
+      <c r="L206" t="n">
+        <v>2.75</v>
+      </c>
       <c r="M206" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="N206" t="inlineStr"/>
+      <c r="N206" t="n">
+        <v>76.3</v>
+      </c>
       <c r="O206" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P206" t="n">
-        <v>-12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="207">
@@ -12490,34 +12316,38 @@
         <v>5</v>
       </c>
       <c r="G207" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>William Dewhirst (IRE)</t>
+          <t>Bay Breeze</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J207" t="n">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="K207" t="n">
-        <v>72</v>
-      </c>
-      <c r="L207" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="L207" t="n">
+        <v>7</v>
+      </c>
       <c r="M207" t="n">
         <v>70.48999999999999</v>
       </c>
-      <c r="N207" t="inlineStr"/>
+      <c r="N207" t="n">
+        <v>55.8</v>
+      </c>
       <c r="O207" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
       <c r="P207" t="n">
-        <v>-12</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="208">
@@ -12546,28 +12376,30 @@
         <v>5</v>
       </c>
       <c r="G208" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Glory Hyde (IRE)</t>
+          <t>Keldeo</t>
         </is>
       </c>
       <c r="I208" t="n">
         <v>5</v>
       </c>
       <c r="J208" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K208" t="n">
-        <v>68</v>
-      </c>
-      <c r="L208" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="L208" t="n">
+        <v>7.029999999999999</v>
+      </c>
       <c r="M208" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="N208" t="n">
-        <v>79.8</v>
+        <v>62.2</v>
       </c>
       <c r="O208" t="inlineStr">
         <is>
@@ -12575,7 +12407,7 @@
         </is>
       </c>
       <c r="P208" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="209">
@@ -12604,30 +12436,30 @@
         <v>5</v>
       </c>
       <c r="G209" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Magic Boy (GER)</t>
+          <t>Cairdeas</t>
         </is>
       </c>
       <c r="I209" t="n">
         <v>4</v>
       </c>
       <c r="J209" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K209" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L209" t="n">
-        <v>2.75</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="M209" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="N209" t="n">
-        <v>76.3</v>
+        <v>57.3</v>
       </c>
       <c r="O209" t="inlineStr">
         <is>
@@ -12635,7 +12467,7 @@
         </is>
       </c>
       <c r="P209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="210">
@@ -12664,30 +12496,30 @@
         <v>5</v>
       </c>
       <c r="G210" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Bay Breeze</t>
+          <t>Beattie Is Back</t>
         </is>
       </c>
       <c r="I210" t="n">
         <v>7</v>
       </c>
       <c r="J210" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="K210" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="L210" t="n">
-        <v>7</v>
+        <v>10.28</v>
       </c>
       <c r="M210" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="N210" t="n">
-        <v>55.8</v>
+        <v>48.5</v>
       </c>
       <c r="O210" t="inlineStr">
         <is>
@@ -12695,7 +12527,7 @@
         </is>
       </c>
       <c r="P210" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="211">
@@ -12724,30 +12556,30 @@
         <v>5</v>
       </c>
       <c r="G211" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Keldeo</t>
+          <t>Fortamour (IRE)</t>
         </is>
       </c>
       <c r="I211" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J211" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="K211" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="L211" t="n">
-        <v>7.03</v>
+        <v>10.78</v>
       </c>
       <c r="M211" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="N211" t="n">
-        <v>62.2</v>
+        <v>48.6</v>
       </c>
       <c r="O211" t="inlineStr">
         <is>
@@ -12784,30 +12616,30 @@
         <v>5</v>
       </c>
       <c r="G212" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Cairdeas</t>
+          <t>Blazing Son</t>
         </is>
       </c>
       <c r="I212" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J212" t="n">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="K212" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="L212" t="n">
-        <v>8.279999999999999</v>
+        <v>11.53</v>
       </c>
       <c r="M212" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="N212" t="n">
-        <v>57.3</v>
+        <v>40.3</v>
       </c>
       <c r="O212" t="inlineStr">
         <is>
@@ -12815,7 +12647,7 @@
         </is>
       </c>
       <c r="P212" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="213">
@@ -12844,30 +12676,30 @@
         <v>5</v>
       </c>
       <c r="G213" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Beattie Is Back</t>
+          <t>Men Of Honour (IRE)</t>
         </is>
       </c>
       <c r="I213" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J213" t="n">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="K213" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="L213" t="n">
-        <v>10.28</v>
+        <v>12.53</v>
       </c>
       <c r="M213" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="N213" t="n">
-        <v>51.9</v>
+        <v>41.9</v>
       </c>
       <c r="O213" t="inlineStr">
         <is>
@@ -12875,7 +12707,7 @@
         </is>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="214">
@@ -12904,30 +12736,30 @@
         <v>5</v>
       </c>
       <c r="G214" t="n">
+        <v>10</v>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Miss Willows</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
         <v>7</v>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Fortamour (IRE)</t>
-        </is>
-      </c>
-      <c r="I214" t="n">
-        <v>10</v>
-      </c>
       <c r="J214" t="n">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="K214" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="L214" t="n">
-        <v>10.78</v>
+        <v>17.28</v>
       </c>
       <c r="M214" t="n">
         <v>70.48999999999999</v>
       </c>
       <c r="N214" t="n">
-        <v>48.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="O214" t="inlineStr">
         <is>
@@ -12963,40 +12795,24 @@
       <c r="F215" t="n">
         <v>5</v>
       </c>
-      <c r="G215" t="n">
-        <v>8</v>
-      </c>
+      <c r="G215" t="inlineStr"/>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Blazing Son</t>
-        </is>
-      </c>
-      <c r="I215" t="n">
-        <v>8</v>
-      </c>
-      <c r="J215" t="n">
-        <v>132</v>
-      </c>
-      <c r="K215" t="n">
-        <v>72</v>
-      </c>
-      <c r="L215" t="n">
-        <v>11.53</v>
-      </c>
-      <c r="M215" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="N215" t="n">
-        <v>45.3</v>
-      </c>
+          <t>Raft Up (IRE)</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr"/>
+      <c r="J215" t="inlineStr"/>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
+      <c r="M215" t="inlineStr"/>
+      <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P215" t="n">
-        <v>0</v>
-      </c>
+      <c r="P215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13023,40 +12839,24 @@
       <c r="F216" t="n">
         <v>5</v>
       </c>
-      <c r="G216" t="n">
-        <v>9</v>
-      </c>
+      <c r="G216" t="inlineStr"/>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Men Of Honour (IRE)</t>
-        </is>
-      </c>
-      <c r="I216" t="n">
-        <v>4</v>
-      </c>
-      <c r="J216" t="n">
-        <v>130</v>
-      </c>
-      <c r="K216" t="n">
-        <v>70</v>
-      </c>
-      <c r="L216" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="M216" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="N216" t="n">
-        <v>41.9</v>
-      </c>
+          <t>William Dewhirst (IRE)</t>
+        </is>
+      </c>
+      <c r="I216" t="inlineStr"/>
+      <c r="J216" t="inlineStr"/>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
+      <c r="M216" t="inlineStr"/>
+      <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P216" t="n">
-        <v>0</v>
-      </c>
+      <c r="P216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -13083,40 +12883,24 @@
       <c r="F217" t="n">
         <v>5</v>
       </c>
-      <c r="G217" t="n">
-        <v>10</v>
-      </c>
+      <c r="G217" t="inlineStr"/>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Miss Willows</t>
-        </is>
-      </c>
-      <c r="I217" t="n">
-        <v>7</v>
-      </c>
-      <c r="J217" t="n">
-        <v>117</v>
-      </c>
-      <c r="K217" t="n">
-        <v>57</v>
-      </c>
-      <c r="L217" t="n">
-        <v>17.28</v>
-      </c>
-      <c r="M217" t="n">
-        <v>70.48999999999999</v>
-      </c>
-      <c r="N217" t="n">
-        <v>11.6</v>
-      </c>
+          <t>Blind Beggar (IRE)</t>
+        </is>
+      </c>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
+      <c r="M217" t="inlineStr"/>
+      <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="P217" t="n">
-        <v>0</v>
-      </c>
+      <c r="P217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13393,7 +13177,7 @@
         <v>7</v>
       </c>
       <c r="J222" t="n">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="K222" t="n">
         <v>59</v>
@@ -13405,7 +13189,7 @@
         <v>58.17</v>
       </c>
       <c r="N222" t="n">
-        <v>53.8</v>
+        <v>49.7</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
@@ -13413,7 +13197,7 @@
         </is>
       </c>
       <c r="P222" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="223">
@@ -13533,7 +13317,7 @@
         </is>
       </c>
       <c r="P224" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="225">
@@ -13573,7 +13357,7 @@
         <v>7</v>
       </c>
       <c r="J225" t="n">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="K225" t="n">
         <v>67</v>
@@ -13585,7 +13369,7 @@
         <v>58.17</v>
       </c>
       <c r="N225" t="n">
-        <v>0.8</v>
+        <v>-3.7</v>
       </c>
       <c r="O225" t="inlineStr">
         <is>
@@ -13751,7 +13535,7 @@
         <v>3</v>
       </c>
       <c r="J228" t="n">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="K228" t="n">
         <v>64</v>
@@ -13763,7 +13547,7 @@
         <v>100.45</v>
       </c>
       <c r="N228" t="n">
-        <v>73.3</v>
+        <v>70.2</v>
       </c>
       <c r="O228" t="inlineStr">
         <is>
@@ -13771,7 +13555,7 @@
         </is>
       </c>
       <c r="P228" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="229">
@@ -13831,7 +13615,7 @@
         </is>
       </c>
       <c r="P229" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="230">
